--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 16:45</t>
+    <t xml:space="preserve">2026-09-09 19:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:11</t>
+    <t xml:space="preserve">2026-09-17 04:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:26</t>
+    <t xml:space="preserve">2026-09-25 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:20</t>
+    <t xml:space="preserve">2026-09-26 23:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2024_coquimbo_provincial.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:53</t>
+    <t xml:space="preserve">2026-10-05 05:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
